--- a/data/tweet_hourly_wide.xlsx
+++ b/data/tweet_hourly_wide.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyPythonProjects\Polymarket_Analysis\data\exports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyPythonProjects\Polymarket_Analysis\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="12855" windowHeight="11685"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="8">
   <si>
     <t>Sun</t>
   </si>
@@ -673,7 +673,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -690,9 +690,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1220,16 +1217,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:HS27"/>
+  <dimension ref="A1:IN27"/>
   <sheetFormatPr defaultColWidth="8.725" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="6.18333333333333" customWidth="1"/>
-    <col min="2" max="139" width="4.725" customWidth="1"/>
-    <col min="140" max="140" width="4.725" style="1" customWidth="1"/>
-    <col min="141" max="227" width="4.725" customWidth="1"/>
+    <col min="2" max="139" width="4.625" customWidth="1"/>
+    <col min="140" max="140" width="4.625" style="1" customWidth="1"/>
+    <col min="141" max="249" width="4.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:227">
+    <row r="1" spans="1:248">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -1908,8 +1905,71 @@
       <c r="HS1" t="s">
         <v>1</v>
       </c>
+      <c r="HT1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="HU1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="HV1" t="s">
+        <v>4</v>
+      </c>
+      <c r="HW1" t="s">
+        <v>5</v>
+      </c>
+      <c r="HX1" t="s">
+        <v>6</v>
+      </c>
+      <c r="HY1" t="s">
+        <v>0</v>
+      </c>
+      <c r="HZ1" t="s">
+        <v>1</v>
+      </c>
+      <c r="IA1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="IB1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="IC1" t="s">
+        <v>4</v>
+      </c>
+      <c r="ID1" t="s">
+        <v>5</v>
+      </c>
+      <c r="IE1" t="s">
+        <v>6</v>
+      </c>
+      <c r="IF1" t="s">
+        <v>0</v>
+      </c>
+      <c r="IG1" t="s">
+        <v>1</v>
+      </c>
+      <c r="IH1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="II1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="IJ1" t="s">
+        <v>4</v>
+      </c>
+      <c r="IK1" t="s">
+        <v>5</v>
+      </c>
+      <c r="IL1" t="s">
+        <v>6</v>
+      </c>
+      <c r="IM1" t="s">
+        <v>0</v>
+      </c>
+      <c r="IN1" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="2" spans="1:227">
+    <row r="2" spans="1:248">
       <c r="B2" s="3">
         <v>46033</v>
       </c>
@@ -2588,8 +2648,71 @@
       <c r="HS2" s="3">
         <v>46258</v>
       </c>
+      <c r="HT2" s="3">
+        <v>46259</v>
+      </c>
+      <c r="HU2" s="3">
+        <v>46260</v>
+      </c>
+      <c r="HV2" s="3">
+        <v>46261</v>
+      </c>
+      <c r="HW2" s="3">
+        <v>46262</v>
+      </c>
+      <c r="HX2" s="3">
+        <v>46263</v>
+      </c>
+      <c r="HY2" s="3">
+        <v>46264</v>
+      </c>
+      <c r="HZ2" s="3">
+        <v>46265</v>
+      </c>
+      <c r="IA2" s="3">
+        <v>46266</v>
+      </c>
+      <c r="IB2" s="3">
+        <v>46267</v>
+      </c>
+      <c r="IC2" s="3">
+        <v>46268</v>
+      </c>
+      <c r="ID2" s="3">
+        <v>46269</v>
+      </c>
+      <c r="IE2" s="3">
+        <v>46270</v>
+      </c>
+      <c r="IF2" s="3">
+        <v>46271</v>
+      </c>
+      <c r="IG2" s="3">
+        <v>46272</v>
+      </c>
+      <c r="IH2" s="3">
+        <v>46273</v>
+      </c>
+      <c r="II2" s="3">
+        <v>46274</v>
+      </c>
+      <c r="IJ2" s="3">
+        <v>46275</v>
+      </c>
+      <c r="IK2" s="3">
+        <v>46276</v>
+      </c>
+      <c r="IL2" s="3">
+        <v>46277</v>
+      </c>
+      <c r="IM2" s="3">
+        <v>46278</v>
+      </c>
+      <c r="IN2" s="3">
+        <v>46279</v>
+      </c>
     </row>
-    <row r="3" spans="1:227">
+    <row r="3" spans="1:248">
       <c r="A3" s="5">
         <v>0</v>
       </c>
@@ -3251,10 +3374,64 @@
         <v>1</v>
       </c>
       <c r="HN3">
+        <v>9</v>
+      </c>
+      <c r="HO3">
+        <v>12</v>
+      </c>
+      <c r="HP3">
+        <v>1</v>
+      </c>
+      <c r="HQ3">
+        <v>0</v>
+      </c>
+      <c r="HR3">
+        <v>0</v>
+      </c>
+      <c r="HS3">
+        <v>0</v>
+      </c>
+      <c r="HT3">
+        <v>4</v>
+      </c>
+      <c r="HU3">
+        <v>0</v>
+      </c>
+      <c r="HV3">
+        <v>1</v>
+      </c>
+      <c r="HW3">
+        <v>0</v>
+      </c>
+      <c r="HX3">
+        <v>0</v>
+      </c>
+      <c r="HY3">
+        <v>0</v>
+      </c>
+      <c r="HZ3">
+        <v>0</v>
+      </c>
+      <c r="IA3">
+        <v>0</v>
+      </c>
+      <c r="IB3">
+        <v>0</v>
+      </c>
+      <c r="IC3">
+        <v>18</v>
+      </c>
+      <c r="ID3">
+        <v>0</v>
+      </c>
+      <c r="IE3">
+        <v>1</v>
+      </c>
+      <c r="IF3">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:227">
+    <row r="4" spans="1:248">
       <c r="A4" s="5">
         <v>0.0416666666666667</v>
       </c>
@@ -3916,10 +4093,64 @@
         <v>3</v>
       </c>
       <c r="HN4">
+        <v>8</v>
+      </c>
+      <c r="HO4">
+        <v>12</v>
+      </c>
+      <c r="HP4">
+        <v>0</v>
+      </c>
+      <c r="HQ4">
+        <v>0</v>
+      </c>
+      <c r="HR4">
+        <v>0</v>
+      </c>
+      <c r="HS4">
+        <v>0</v>
+      </c>
+      <c r="HT4">
+        <v>0</v>
+      </c>
+      <c r="HU4">
+        <v>2</v>
+      </c>
+      <c r="HV4">
+        <v>0</v>
+      </c>
+      <c r="HW4">
+        <v>2</v>
+      </c>
+      <c r="HX4">
+        <v>7</v>
+      </c>
+      <c r="HY4">
+        <v>0</v>
+      </c>
+      <c r="HZ4">
+        <v>0</v>
+      </c>
+      <c r="IA4">
+        <v>0</v>
+      </c>
+      <c r="IB4">
+        <v>3</v>
+      </c>
+      <c r="IC4">
+        <v>8</v>
+      </c>
+      <c r="ID4">
+        <v>0</v>
+      </c>
+      <c r="IE4">
+        <v>0</v>
+      </c>
+      <c r="IF4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:227">
+    <row r="5" spans="1:248">
       <c r="A5" s="5">
         <v>0.0833333333333333</v>
       </c>
@@ -4581,10 +4812,64 @@
         <v>0</v>
       </c>
       <c r="HN5">
+        <v>3</v>
+      </c>
+      <c r="HO5">
+        <v>0</v>
+      </c>
+      <c r="HP5">
+        <v>0</v>
+      </c>
+      <c r="HQ5">
+        <v>0</v>
+      </c>
+      <c r="HR5">
+        <v>0</v>
+      </c>
+      <c r="HS5">
+        <v>0</v>
+      </c>
+      <c r="HT5">
+        <v>1</v>
+      </c>
+      <c r="HU5">
+        <v>0</v>
+      </c>
+      <c r="HV5">
+        <v>3</v>
+      </c>
+      <c r="HW5">
+        <v>0</v>
+      </c>
+      <c r="HX5">
+        <v>0</v>
+      </c>
+      <c r="HY5">
+        <v>2</v>
+      </c>
+      <c r="HZ5">
+        <v>0</v>
+      </c>
+      <c r="IA5">
+        <v>0</v>
+      </c>
+      <c r="IB5">
+        <v>2</v>
+      </c>
+      <c r="IC5">
+        <v>0</v>
+      </c>
+      <c r="ID5">
+        <v>1</v>
+      </c>
+      <c r="IE5">
+        <v>6</v>
+      </c>
+      <c r="IF5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:227">
+    <row r="6" spans="1:248">
       <c r="A6" s="5">
         <v>0.125</v>
       </c>
@@ -5249,10 +5534,64 @@
         <v>0</v>
       </c>
       <c r="HN6">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HO6">
+        <v>0</v>
+      </c>
+      <c r="HP6">
+        <v>0</v>
+      </c>
+      <c r="HQ6">
+        <v>0</v>
+      </c>
+      <c r="HR6">
+        <v>0</v>
+      </c>
+      <c r="HS6">
+        <v>0</v>
+      </c>
+      <c r="HT6">
+        <v>1</v>
+      </c>
+      <c r="HU6">
+        <v>0</v>
+      </c>
+      <c r="HV6">
+        <v>0</v>
+      </c>
+      <c r="HW6">
+        <v>0</v>
+      </c>
+      <c r="HX6">
+        <v>2</v>
+      </c>
+      <c r="HY6">
+        <v>2</v>
+      </c>
+      <c r="HZ6">
+        <v>0</v>
+      </c>
+      <c r="IA6">
+        <v>0</v>
+      </c>
+      <c r="IB6">
+        <v>4</v>
+      </c>
+      <c r="IC6">
+        <v>0</v>
+      </c>
+      <c r="ID6">
+        <v>0</v>
+      </c>
+      <c r="IE6">
+        <v>4</v>
+      </c>
+      <c r="IF6">
+        <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:227">
+    <row r="7" spans="1:248">
       <c r="A7" s="5">
         <v>0.166666666666667</v>
       </c>
@@ -5917,10 +6256,64 @@
         <v>0</v>
       </c>
       <c r="HN7">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="HO7">
+        <v>0</v>
+      </c>
+      <c r="HP7">
+        <v>0</v>
+      </c>
+      <c r="HQ7">
+        <v>0</v>
+      </c>
+      <c r="HR7">
+        <v>0</v>
+      </c>
+      <c r="HS7">
+        <v>0</v>
+      </c>
+      <c r="HT7">
+        <v>0</v>
+      </c>
+      <c r="HU7">
+        <v>0</v>
+      </c>
+      <c r="HV7">
+        <v>0</v>
+      </c>
+      <c r="HW7">
+        <v>0</v>
+      </c>
+      <c r="HX7">
+        <v>3</v>
+      </c>
+      <c r="HY7">
+        <v>1</v>
+      </c>
+      <c r="HZ7">
+        <v>2</v>
+      </c>
+      <c r="IA7">
+        <v>0</v>
+      </c>
+      <c r="IB7">
+        <v>1</v>
+      </c>
+      <c r="IC7">
+        <v>0</v>
+      </c>
+      <c r="ID7">
+        <v>1</v>
+      </c>
+      <c r="IE7">
+        <v>0</v>
+      </c>
+      <c r="IF7">
+        <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:227">
+    <row r="8" spans="1:248">
       <c r="A8" s="5">
         <v>0.208333333333333</v>
       </c>
@@ -6587,8 +6980,62 @@
       <c r="HN8">
         <v>0</v>
       </c>
+      <c r="HO8">
+        <v>0</v>
+      </c>
+      <c r="HP8">
+        <v>0</v>
+      </c>
+      <c r="HQ8">
+        <v>0</v>
+      </c>
+      <c r="HR8">
+        <v>0</v>
+      </c>
+      <c r="HS8">
+        <v>0</v>
+      </c>
+      <c r="HT8">
+        <v>0</v>
+      </c>
+      <c r="HU8">
+        <v>0</v>
+      </c>
+      <c r="HV8">
+        <v>0</v>
+      </c>
+      <c r="HW8">
+        <v>0</v>
+      </c>
+      <c r="HX8">
+        <v>1</v>
+      </c>
+      <c r="HY8">
+        <v>0</v>
+      </c>
+      <c r="HZ8">
+        <v>2</v>
+      </c>
+      <c r="IA8">
+        <v>0</v>
+      </c>
+      <c r="IB8">
+        <v>0</v>
+      </c>
+      <c r="IC8">
+        <v>0</v>
+      </c>
+      <c r="ID8">
+        <v>0</v>
+      </c>
+      <c r="IE8">
+        <v>0</v>
+      </c>
+      <c r="IF8">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:227">
+    <row r="9" spans="1:248">
       <c r="A9" s="5">
         <v>0.25</v>
       </c>
@@ -7255,8 +7702,62 @@
       <c r="HN9">
         <v>0</v>
       </c>
+      <c r="HO9">
+        <v>11</v>
+      </c>
+      <c r="HP9">
+        <v>0</v>
+      </c>
+      <c r="HQ9">
+        <v>0</v>
+      </c>
+      <c r="HR9">
+        <v>8</v>
+      </c>
+      <c r="HS9">
+        <v>0</v>
+      </c>
+      <c r="HT9">
+        <v>0</v>
+      </c>
+      <c r="HU9">
+        <v>0</v>
+      </c>
+      <c r="HV9">
+        <v>0</v>
+      </c>
+      <c r="HW9">
+        <v>0</v>
+      </c>
+      <c r="HX9">
+        <v>0</v>
+      </c>
+      <c r="HY9">
+        <v>0</v>
+      </c>
+      <c r="HZ9">
+        <v>1</v>
+      </c>
+      <c r="IA9">
+        <v>0</v>
+      </c>
+      <c r="IB9">
+        <v>0</v>
+      </c>
+      <c r="IC9">
+        <v>0</v>
+      </c>
+      <c r="ID9">
+        <v>0</v>
+      </c>
+      <c r="IE9">
+        <v>0</v>
+      </c>
+      <c r="IF9">
+        <v>0</v>
+      </c>
     </row>
-    <row r="10" spans="1:227">
+    <row r="10" spans="1:248">
       <c r="A10" s="5">
         <v>0.291666666666667</v>
       </c>
@@ -7920,8 +8421,62 @@
       <c r="HN10">
         <v>0</v>
       </c>
+      <c r="HO10">
+        <v>13</v>
+      </c>
+      <c r="HP10">
+        <v>0</v>
+      </c>
+      <c r="HQ10">
+        <v>0</v>
+      </c>
+      <c r="HR10">
+        <v>0</v>
+      </c>
+      <c r="HS10">
+        <v>0</v>
+      </c>
+      <c r="HT10">
+        <v>0</v>
+      </c>
+      <c r="HU10">
+        <v>0</v>
+      </c>
+      <c r="HV10">
+        <v>0</v>
+      </c>
+      <c r="HW10">
+        <v>0</v>
+      </c>
+      <c r="HX10">
+        <v>0</v>
+      </c>
+      <c r="HY10">
+        <v>0</v>
+      </c>
+      <c r="HZ10">
+        <v>0</v>
+      </c>
+      <c r="IA10">
+        <v>0</v>
+      </c>
+      <c r="IB10">
+        <v>0</v>
+      </c>
+      <c r="IC10">
+        <v>0</v>
+      </c>
+      <c r="ID10">
+        <v>0</v>
+      </c>
+      <c r="IE10">
+        <v>0</v>
+      </c>
+      <c r="IF10">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="1:227">
+    <row r="11" spans="1:248">
       <c r="A11" s="5">
         <v>0.333333333333333</v>
       </c>
@@ -8588,8 +9143,62 @@
       <c r="HN11">
         <v>0</v>
       </c>
+      <c r="HO11">
+        <v>0</v>
+      </c>
+      <c r="HP11">
+        <v>0</v>
+      </c>
+      <c r="HQ11">
+        <v>0</v>
+      </c>
+      <c r="HR11">
+        <v>0</v>
+      </c>
+      <c r="HS11">
+        <v>0</v>
+      </c>
+      <c r="HT11">
+        <v>0</v>
+      </c>
+      <c r="HU11">
+        <v>0</v>
+      </c>
+      <c r="HV11">
+        <v>0</v>
+      </c>
+      <c r="HW11">
+        <v>0</v>
+      </c>
+      <c r="HX11">
+        <v>0</v>
+      </c>
+      <c r="HY11">
+        <v>0</v>
+      </c>
+      <c r="HZ11">
+        <v>0</v>
+      </c>
+      <c r="IA11">
+        <v>0</v>
+      </c>
+      <c r="IB11">
+        <v>0</v>
+      </c>
+      <c r="IC11">
+        <v>0</v>
+      </c>
+      <c r="ID11">
+        <v>0</v>
+      </c>
+      <c r="IE11">
+        <v>0</v>
+      </c>
+      <c r="IF11">
+        <v>0</v>
+      </c>
     </row>
-    <row r="12" spans="1:227">
+    <row r="12" spans="1:248">
       <c r="A12" s="5">
         <v>0.375</v>
       </c>
@@ -9256,8 +9865,62 @@
       <c r="HN12">
         <v>0</v>
       </c>
+      <c r="HO12">
+        <v>0</v>
+      </c>
+      <c r="HP12">
+        <v>0</v>
+      </c>
+      <c r="HQ12">
+        <v>0</v>
+      </c>
+      <c r="HR12">
+        <v>0</v>
+      </c>
+      <c r="HS12">
+        <v>1</v>
+      </c>
+      <c r="HT12">
+        <v>0</v>
+      </c>
+      <c r="HU12">
+        <v>0</v>
+      </c>
+      <c r="HV12">
+        <v>0</v>
+      </c>
+      <c r="HW12">
+        <v>0</v>
+      </c>
+      <c r="HX12">
+        <v>0</v>
+      </c>
+      <c r="HY12">
+        <v>0</v>
+      </c>
+      <c r="HZ12">
+        <v>0</v>
+      </c>
+      <c r="IA12">
+        <v>1</v>
+      </c>
+      <c r="IB12">
+        <v>0</v>
+      </c>
+      <c r="IC12">
+        <v>2</v>
+      </c>
+      <c r="ID12">
+        <v>1</v>
+      </c>
+      <c r="IE12">
+        <v>0</v>
+      </c>
+      <c r="IF12">
+        <v>0</v>
+      </c>
     </row>
-    <row r="13" spans="1:227">
+    <row r="13" spans="1:248">
       <c r="A13" s="5">
         <v>0.416666666666667</v>
       </c>
@@ -9922,10 +10585,64 @@
         <v>3</v>
       </c>
       <c r="HN13">
+        <v>9</v>
+      </c>
+      <c r="HO13">
+        <v>0</v>
+      </c>
+      <c r="HP13">
+        <v>0</v>
+      </c>
+      <c r="HQ13">
+        <v>0</v>
+      </c>
+      <c r="HR13">
+        <v>0</v>
+      </c>
+      <c r="HS13">
+        <v>0</v>
+      </c>
+      <c r="HT13">
+        <v>0</v>
+      </c>
+      <c r="HU13">
+        <v>0</v>
+      </c>
+      <c r="HV13">
+        <v>1</v>
+      </c>
+      <c r="HW13">
+        <v>1</v>
+      </c>
+      <c r="HX13">
+        <v>0</v>
+      </c>
+      <c r="HY13">
+        <v>2</v>
+      </c>
+      <c r="HZ13">
+        <v>0</v>
+      </c>
+      <c r="IA13">
+        <v>2</v>
+      </c>
+      <c r="IB13">
+        <v>0</v>
+      </c>
+      <c r="IC13">
+        <v>3</v>
+      </c>
+      <c r="ID13">
+        <v>6</v>
+      </c>
+      <c r="IE13">
+        <v>1</v>
+      </c>
+      <c r="IF13">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:227">
+    <row r="14" spans="1:248">
       <c r="A14" s="5">
         <v>0.458333333333333</v>
       </c>
@@ -10590,10 +11307,64 @@
         <v>0</v>
       </c>
       <c r="HN14">
+        <v>11</v>
+      </c>
+      <c r="HO14">
+        <v>0</v>
+      </c>
+      <c r="HP14">
+        <v>1</v>
+      </c>
+      <c r="HQ14">
+        <v>6</v>
+      </c>
+      <c r="HR14">
+        <v>0</v>
+      </c>
+      <c r="HS14">
+        <v>4</v>
+      </c>
+      <c r="HT14">
+        <v>2</v>
+      </c>
+      <c r="HU14">
+        <v>0</v>
+      </c>
+      <c r="HV14">
+        <v>1</v>
+      </c>
+      <c r="HW14">
+        <v>0</v>
+      </c>
+      <c r="HX14">
+        <v>0</v>
+      </c>
+      <c r="HY14">
+        <v>4</v>
+      </c>
+      <c r="HZ14">
+        <v>0</v>
+      </c>
+      <c r="IA14">
+        <v>13</v>
+      </c>
+      <c r="IB14">
+        <v>0</v>
+      </c>
+      <c r="IC14">
+        <v>7</v>
+      </c>
+      <c r="ID14">
+        <v>4</v>
+      </c>
+      <c r="IE14">
+        <v>2</v>
+      </c>
+      <c r="IF14">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:227">
+    <row r="15" spans="1:248">
       <c r="A15" s="5">
         <v>0.5</v>
       </c>
@@ -11258,10 +12029,64 @@
         <v>7</v>
       </c>
       <c r="HN15">
+        <v>3</v>
+      </c>
+      <c r="HO15">
+        <v>7</v>
+      </c>
+      <c r="HP15">
+        <v>8</v>
+      </c>
+      <c r="HQ15">
+        <v>1</v>
+      </c>
+      <c r="HR15">
+        <v>1</v>
+      </c>
+      <c r="HS15">
+        <v>0</v>
+      </c>
+      <c r="HT15">
+        <v>5</v>
+      </c>
+      <c r="HU15">
+        <v>0</v>
+      </c>
+      <c r="HV15">
+        <v>0</v>
+      </c>
+      <c r="HW15">
+        <v>0</v>
+      </c>
+      <c r="HX15">
+        <v>2</v>
+      </c>
+      <c r="HY15">
+        <v>1</v>
+      </c>
+      <c r="HZ15">
+        <v>0</v>
+      </c>
+      <c r="IA15">
+        <v>7</v>
+      </c>
+      <c r="IB15">
+        <v>0</v>
+      </c>
+      <c r="IC15">
+        <v>0</v>
+      </c>
+      <c r="ID15">
+        <v>0</v>
+      </c>
+      <c r="IE15">
+        <v>0</v>
+      </c>
+      <c r="IF15">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:227">
+    <row r="16" spans="1:248">
       <c r="A16" s="5">
         <v>0.541666666666667</v>
       </c>
@@ -11926,10 +12751,64 @@
         <v>0</v>
       </c>
       <c r="HN16">
+        <v>8</v>
+      </c>
+      <c r="HO16">
+        <v>10</v>
+      </c>
+      <c r="HP16">
+        <v>1</v>
+      </c>
+      <c r="HQ16">
+        <v>2</v>
+      </c>
+      <c r="HR16">
+        <v>3</v>
+      </c>
+      <c r="HS16">
+        <v>10</v>
+      </c>
+      <c r="HT16">
+        <v>7</v>
+      </c>
+      <c r="HU16">
+        <v>0</v>
+      </c>
+      <c r="HV16">
+        <v>3</v>
+      </c>
+      <c r="HW16">
+        <v>0</v>
+      </c>
+      <c r="HX16">
+        <v>0</v>
+      </c>
+      <c r="HY16">
+        <v>0</v>
+      </c>
+      <c r="HZ16">
+        <v>0</v>
+      </c>
+      <c r="IA16">
+        <v>0</v>
+      </c>
+      <c r="IB16">
+        <v>4</v>
+      </c>
+      <c r="IC16">
+        <v>0</v>
+      </c>
+      <c r="ID16">
+        <v>0</v>
+      </c>
+      <c r="IE16">
+        <v>4</v>
+      </c>
+      <c r="IF16">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:222">
+    <row r="17" spans="1:240">
       <c r="A17" s="5">
         <v>0.583333333333333</v>
       </c>
@@ -12594,10 +13473,64 @@
         <v>1</v>
       </c>
       <c r="HN17">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="HO17">
+        <v>0</v>
+      </c>
+      <c r="HP17">
+        <v>1</v>
+      </c>
+      <c r="HQ17">
+        <v>1</v>
+      </c>
+      <c r="HR17">
+        <v>5</v>
+      </c>
+      <c r="HS17">
+        <v>3</v>
+      </c>
+      <c r="HT17">
+        <v>2</v>
+      </c>
+      <c r="HU17">
+        <v>0</v>
+      </c>
+      <c r="HV17">
+        <v>0</v>
+      </c>
+      <c r="HW17">
+        <v>4</v>
+      </c>
+      <c r="HX17">
+        <v>3</v>
+      </c>
+      <c r="HY17">
+        <v>5</v>
+      </c>
+      <c r="HZ17">
+        <v>1</v>
+      </c>
+      <c r="IA17">
+        <v>4</v>
+      </c>
+      <c r="IB17">
+        <v>2</v>
+      </c>
+      <c r="IC17">
+        <v>4</v>
+      </c>
+      <c r="ID17">
+        <v>4</v>
+      </c>
+      <c r="IE17">
+        <v>0</v>
+      </c>
+      <c r="IF17">
+        <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:222">
+    <row r="18" spans="1:240">
       <c r="A18" s="5">
         <v>0.625</v>
       </c>
@@ -13262,10 +14195,64 @@
         <v>4</v>
       </c>
       <c r="HN18">
+        <v>3</v>
+      </c>
+      <c r="HO18">
+        <v>0</v>
+      </c>
+      <c r="HP18">
+        <v>0</v>
+      </c>
+      <c r="HQ18">
+        <v>3</v>
+      </c>
+      <c r="HR18">
+        <v>1</v>
+      </c>
+      <c r="HS18">
+        <v>2</v>
+      </c>
+      <c r="HT18">
+        <v>1</v>
+      </c>
+      <c r="HU18">
+        <v>3</v>
+      </c>
+      <c r="HV18">
+        <v>10</v>
+      </c>
+      <c r="HW18">
+        <v>1</v>
+      </c>
+      <c r="HX18">
+        <v>1</v>
+      </c>
+      <c r="HY18">
+        <v>4</v>
+      </c>
+      <c r="HZ18">
+        <v>0</v>
+      </c>
+      <c r="IA18">
+        <v>1</v>
+      </c>
+      <c r="IB18">
+        <v>0</v>
+      </c>
+      <c r="IC18">
+        <v>3</v>
+      </c>
+      <c r="ID18">
+        <v>0</v>
+      </c>
+      <c r="IE18">
+        <v>0</v>
+      </c>
+      <c r="IF18">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:222">
+    <row r="19" spans="1:240">
       <c r="A19" s="5">
         <v>0.666666666666667</v>
       </c>
@@ -13932,8 +14919,62 @@
       <c r="HN19">
         <v>0</v>
       </c>
+      <c r="HO19">
+        <v>2</v>
+      </c>
+      <c r="HP19">
+        <v>2</v>
+      </c>
+      <c r="HQ19">
+        <v>1</v>
+      </c>
+      <c r="HR19">
+        <v>4</v>
+      </c>
+      <c r="HS19">
+        <v>1</v>
+      </c>
+      <c r="HT19">
+        <v>0</v>
+      </c>
+      <c r="HU19">
+        <v>0</v>
+      </c>
+      <c r="HV19">
+        <v>0</v>
+      </c>
+      <c r="HW19">
+        <v>0</v>
+      </c>
+      <c r="HX19">
+        <v>2</v>
+      </c>
+      <c r="HY19">
+        <v>1</v>
+      </c>
+      <c r="HZ19">
+        <v>0</v>
+      </c>
+      <c r="IA19">
+        <v>1</v>
+      </c>
+      <c r="IB19">
+        <v>0</v>
+      </c>
+      <c r="IC19">
+        <v>4</v>
+      </c>
+      <c r="ID19">
+        <v>0</v>
+      </c>
+      <c r="IE19">
+        <v>3</v>
+      </c>
+      <c r="IF19">
+        <v>0</v>
+      </c>
     </row>
-    <row r="20" spans="1:222">
+    <row r="20" spans="1:240">
       <c r="A20" s="5">
         <v>0.708333333333333</v>
       </c>
@@ -14600,8 +15641,62 @@
       <c r="HN20">
         <v>0</v>
       </c>
+      <c r="HO20">
+        <v>6</v>
+      </c>
+      <c r="HP20">
+        <v>11</v>
+      </c>
+      <c r="HQ20">
+        <v>0</v>
+      </c>
+      <c r="HR20">
+        <v>3</v>
+      </c>
+      <c r="HS20">
+        <v>6</v>
+      </c>
+      <c r="HT20">
+        <v>2</v>
+      </c>
+      <c r="HU20">
+        <v>0</v>
+      </c>
+      <c r="HV20">
+        <v>0</v>
+      </c>
+      <c r="HW20">
+        <v>2</v>
+      </c>
+      <c r="HX20">
+        <v>1</v>
+      </c>
+      <c r="HY20">
+        <v>0</v>
+      </c>
+      <c r="HZ20">
+        <v>1</v>
+      </c>
+      <c r="IA20">
+        <v>0</v>
+      </c>
+      <c r="IB20">
+        <v>0</v>
+      </c>
+      <c r="IC20">
+        <v>0</v>
+      </c>
+      <c r="ID20">
+        <v>5</v>
+      </c>
+      <c r="IE20">
+        <v>0</v>
+      </c>
+      <c r="IF20">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="1:222">
+    <row r="21" spans="1:240">
       <c r="A21" s="5">
         <v>0.75</v>
       </c>
@@ -15268,8 +16363,62 @@
       <c r="HN21">
         <v>0</v>
       </c>
+      <c r="HO21">
+        <v>2</v>
+      </c>
+      <c r="HP21">
+        <v>2</v>
+      </c>
+      <c r="HQ21">
+        <v>0</v>
+      </c>
+      <c r="HR21">
+        <v>3</v>
+      </c>
+      <c r="HS21">
+        <v>1</v>
+      </c>
+      <c r="HT21">
+        <v>0</v>
+      </c>
+      <c r="HU21">
+        <v>0</v>
+      </c>
+      <c r="HV21">
+        <v>0</v>
+      </c>
+      <c r="HW21">
+        <v>6</v>
+      </c>
+      <c r="HX21">
+        <v>0</v>
+      </c>
+      <c r="HY21">
+        <v>0</v>
+      </c>
+      <c r="HZ21">
+        <v>1</v>
+      </c>
+      <c r="IA21">
+        <v>0</v>
+      </c>
+      <c r="IB21">
+        <v>0</v>
+      </c>
+      <c r="IC21">
+        <v>0</v>
+      </c>
+      <c r="ID21">
+        <v>4</v>
+      </c>
+      <c r="IE21">
+        <v>0</v>
+      </c>
+      <c r="IF21">
+        <v>1</v>
+      </c>
     </row>
-    <row r="22" spans="1:222">
+    <row r="22" spans="1:240">
       <c r="A22" s="5">
         <v>0.791666666666667</v>
       </c>
@@ -15934,10 +17083,64 @@
         <v>0</v>
       </c>
       <c r="HN22">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="HO22">
+        <v>5</v>
+      </c>
+      <c r="HP22">
+        <v>6</v>
+      </c>
+      <c r="HQ22">
+        <v>0</v>
+      </c>
+      <c r="HR22">
+        <v>0</v>
+      </c>
+      <c r="HS22">
+        <v>2</v>
+      </c>
+      <c r="HT22">
+        <v>0</v>
+      </c>
+      <c r="HU22">
+        <v>0</v>
+      </c>
+      <c r="HV22">
+        <v>0</v>
+      </c>
+      <c r="HW22">
+        <v>0</v>
+      </c>
+      <c r="HX22">
+        <v>3</v>
+      </c>
+      <c r="HY22">
+        <v>1</v>
+      </c>
+      <c r="HZ22">
+        <v>3</v>
+      </c>
+      <c r="IA22">
+        <v>0</v>
+      </c>
+      <c r="IB22">
+        <v>0</v>
+      </c>
+      <c r="IC22">
+        <v>1</v>
+      </c>
+      <c r="ID22">
+        <v>4</v>
+      </c>
+      <c r="IE22">
+        <v>0</v>
+      </c>
+      <c r="IF22">
+        <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:222">
+    <row r="23" spans="1:240">
       <c r="A23" s="5">
         <v>0.833333333333333</v>
       </c>
@@ -16604,8 +17807,62 @@
       <c r="HN23">
         <v>0</v>
       </c>
+      <c r="HO23">
+        <v>1</v>
+      </c>
+      <c r="HP23">
+        <v>4</v>
+      </c>
+      <c r="HQ23">
+        <v>0</v>
+      </c>
+      <c r="HR23">
+        <v>0</v>
+      </c>
+      <c r="HS23">
+        <v>0</v>
+      </c>
+      <c r="HT23">
+        <v>5</v>
+      </c>
+      <c r="HU23">
+        <v>0</v>
+      </c>
+      <c r="HV23">
+        <v>3</v>
+      </c>
+      <c r="HW23">
+        <v>0</v>
+      </c>
+      <c r="HX23">
+        <v>5</v>
+      </c>
+      <c r="HY23">
+        <v>0</v>
+      </c>
+      <c r="HZ23">
+        <v>7</v>
+      </c>
+      <c r="IA23">
+        <v>0</v>
+      </c>
+      <c r="IB23">
+        <v>0</v>
+      </c>
+      <c r="IC23">
+        <v>2</v>
+      </c>
+      <c r="ID23">
+        <v>0</v>
+      </c>
+      <c r="IE23">
+        <v>4</v>
+      </c>
+      <c r="IF23">
+        <v>0</v>
+      </c>
     </row>
-    <row r="24" spans="1:222">
+    <row r="24" spans="1:240">
       <c r="A24" s="5">
         <v>0.875</v>
       </c>
@@ -17272,8 +18529,62 @@
       <c r="HN24">
         <v>0</v>
       </c>
+      <c r="HO24">
+        <v>2</v>
+      </c>
+      <c r="HP24">
+        <v>5</v>
+      </c>
+      <c r="HQ24">
+        <v>0</v>
+      </c>
+      <c r="HR24">
+        <v>0</v>
+      </c>
+      <c r="HS24">
+        <v>0</v>
+      </c>
+      <c r="HT24">
+        <v>0</v>
+      </c>
+      <c r="HU24">
+        <v>0</v>
+      </c>
+      <c r="HV24">
+        <v>4</v>
+      </c>
+      <c r="HW24">
+        <v>3</v>
+      </c>
+      <c r="HX24">
+        <v>2</v>
+      </c>
+      <c r="HY24">
+        <v>5</v>
+      </c>
+      <c r="HZ24">
+        <v>0</v>
+      </c>
+      <c r="IA24">
+        <v>0</v>
+      </c>
+      <c r="IB24">
+        <v>0</v>
+      </c>
+      <c r="IC24">
+        <v>0</v>
+      </c>
+      <c r="ID24">
+        <v>1</v>
+      </c>
+      <c r="IE24">
+        <v>1</v>
+      </c>
+      <c r="IF24">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="1:222">
+    <row r="25" spans="1:240">
       <c r="A25" s="5">
         <v>0.916666666666667</v>
       </c>
@@ -17938,10 +19249,64 @@
         <v>0</v>
       </c>
       <c r="HN25">
+        <v>1</v>
+      </c>
+      <c r="HO25">
+        <v>2</v>
+      </c>
+      <c r="HP25">
+        <v>2</v>
+      </c>
+      <c r="HQ25">
+        <v>0</v>
+      </c>
+      <c r="HR25">
+        <v>3</v>
+      </c>
+      <c r="HS25">
+        <v>0</v>
+      </c>
+      <c r="HT25">
+        <v>0</v>
+      </c>
+      <c r="HU25">
+        <v>0</v>
+      </c>
+      <c r="HV25">
+        <v>1</v>
+      </c>
+      <c r="HW25">
+        <v>0</v>
+      </c>
+      <c r="HX25">
+        <v>0</v>
+      </c>
+      <c r="HY25">
+        <v>3</v>
+      </c>
+      <c r="HZ25">
+        <v>1</v>
+      </c>
+      <c r="IA25">
+        <v>3</v>
+      </c>
+      <c r="IB25">
+        <v>0</v>
+      </c>
+      <c r="IC25">
+        <v>0</v>
+      </c>
+      <c r="ID25">
+        <v>2</v>
+      </c>
+      <c r="IE25">
+        <v>0</v>
+      </c>
+      <c r="IF25">
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:222">
+    <row r="26" spans="1:240">
       <c r="A26" s="5">
         <v>0.958333333333333</v>
       </c>
@@ -18606,10 +19971,64 @@
         <v>0</v>
       </c>
       <c r="HN26">
+        <v>1</v>
+      </c>
+      <c r="HO26">
+        <v>0</v>
+      </c>
+      <c r="HP26">
+        <v>8</v>
+      </c>
+      <c r="HQ26">
+        <v>0</v>
+      </c>
+      <c r="HR26">
+        <v>0</v>
+      </c>
+      <c r="HS26">
+        <v>0</v>
+      </c>
+      <c r="HT26">
+        <v>0</v>
+      </c>
+      <c r="HU26">
+        <v>0</v>
+      </c>
+      <c r="HV26">
+        <v>0</v>
+      </c>
+      <c r="HW26">
+        <v>0</v>
+      </c>
+      <c r="HX26">
+        <v>1</v>
+      </c>
+      <c r="HY26">
+        <v>2</v>
+      </c>
+      <c r="HZ26">
+        <v>0</v>
+      </c>
+      <c r="IA26">
+        <v>0</v>
+      </c>
+      <c r="IB26">
+        <v>3</v>
+      </c>
+      <c r="IC26">
+        <v>9</v>
+      </c>
+      <c r="ID26">
+        <v>5</v>
+      </c>
+      <c r="IE26">
+        <v>0</v>
+      </c>
+      <c r="IF26">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:222">
+    <row r="27" spans="1:240">
       <c r="A27" t="s">
         <v>7</v>
       </c>
@@ -19161,7 +20580,7 @@
         <f t="shared" si="4"/>
         <v>15</v>
       </c>
-      <c r="EJ27" s="6">
+      <c r="EJ27" s="1">
         <f t="shared" si="4"/>
         <v>31</v>
       </c>
@@ -19491,7 +20910,79 @@
       </c>
       <c r="HN27">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>76</v>
+      </c>
+      <c r="HO27">
+        <f t="shared" ref="HO27:IF27" si="9">SUM(HO3:HO26)</f>
+        <v>85</v>
+      </c>
+      <c r="HP27">
+        <f t="shared" si="9"/>
+        <v>52</v>
+      </c>
+      <c r="HQ27">
+        <f t="shared" si="9"/>
+        <v>14</v>
+      </c>
+      <c r="HR27">
+        <f t="shared" si="9"/>
+        <v>31</v>
+      </c>
+      <c r="HS27">
+        <f t="shared" si="9"/>
+        <v>30</v>
+      </c>
+      <c r="HT27">
+        <f t="shared" si="9"/>
+        <v>30</v>
+      </c>
+      <c r="HU27">
+        <f t="shared" si="9"/>
+        <v>5</v>
+      </c>
+      <c r="HV27">
+        <f t="shared" si="9"/>
+        <v>27</v>
+      </c>
+      <c r="HW27">
+        <f t="shared" si="9"/>
+        <v>19</v>
+      </c>
+      <c r="HX27">
+        <f t="shared" si="9"/>
+        <v>33</v>
+      </c>
+      <c r="HY27">
+        <f t="shared" si="9"/>
+        <v>33</v>
+      </c>
+      <c r="HZ27">
+        <f t="shared" si="9"/>
+        <v>19</v>
+      </c>
+      <c r="IA27">
+        <f t="shared" si="9"/>
+        <v>32</v>
+      </c>
+      <c r="IB27">
+        <f t="shared" si="9"/>
+        <v>19</v>
+      </c>
+      <c r="IC27">
+        <f t="shared" si="9"/>
+        <v>61</v>
+      </c>
+      <c r="ID27">
+        <f t="shared" si="9"/>
+        <v>38</v>
+      </c>
+      <c r="IE27">
+        <f t="shared" si="9"/>
+        <v>26</v>
+      </c>
+      <c r="IF27">
+        <f t="shared" si="9"/>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
